--- a/gte/nodes/LPC/compressor_parameters.xlsx
+++ b/gte/nodes/LPC/compressor_parameters.xlsx
@@ -1060,31 +1060,31 @@
         <v>324.32233271973291</v>
       </c>
       <c r="U3">
-        <v>338.48306208552407</v>
+        <v>337.55316979839438</v>
       </c>
       <c r="V3">
         <v>344.41596054018709</v>
       </c>
       <c r="W3">
-        <v>353.23686971459057</v>
+        <v>353.1730861018118</v>
       </c>
       <c r="X3">
-        <v>83.441196534470748</v>
+        <v>100.47370850249615</v>
       </c>
       <c r="Y3">
         <v>195.15501471521742</v>
       </c>
       <c r="Z3">
-        <v>85.766213788746626</v>
+        <v>87.068003720093884</v>
       </c>
       <c r="AA3">
-        <v>228.58469803600715</v>
+        <v>177.6565286969086</v>
       </c>
       <c r="AB3">
         <v>82.041400712347581</v>
       </c>
       <c r="AC3">
-        <v>181.07898811268564</v>
+        <v>178.97210030089858</v>
       </c>
       <c r="AD3">
         <v>212.81102155928954</v>
@@ -1096,13 +1096,13 @@
         <v>214.41995491565626</v>
       </c>
       <c r="AG3">
-        <v>5.1091309723327304E-15</v>
+        <v>55.969034484618319</v>
       </c>
       <c r="AH3">
         <v>180.19837984810317</v>
       </c>
       <c r="AI3">
-        <v>47.901699647906668</v>
+        <v>50.195285369280967</v>
       </c>
       <c r="AJ3">
         <v>83.441196534470748</v>
@@ -1114,85 +1114,85 @@
         <v>71.142607476102043</v>
       </c>
       <c r="AM3">
-        <v>0.26848825609412141</v>
+        <v>0.32329367146599003</v>
       </c>
       <c r="AN3">
         <v>0.60173165714080812</v>
       </c>
       <c r="AO3">
-        <v>0.26444744976246376</v>
+        <v>0.268461326699123</v>
       </c>
       <c r="AP3">
-        <v>0.24651513142299503</v>
+        <v>0.29765298475053475</v>
       </c>
       <c r="AQ3">
         <v>0.56662593222780211</v>
       </c>
       <c r="AR3">
-        <v>0.24280085444660485</v>
+        <v>0.24653068749127205</v>
       </c>
       <c r="AS3">
-        <v>0.67532093519719749</v>
+        <v>0.52630680020873455</v>
       </c>
       <c r="AT3">
         <v>0.23820441010826743</v>
       </c>
       <c r="AU3">
-        <v>0.5126276548056673</v>
+        <v>0.50675464055407937</v>
       </c>
       <c r="AV3">
-        <v>284.72764761759396</v>
+        <v>283.16536940702974</v>
       </c>
       <c r="AW3">
         <v>294.97364729296476</v>
       </c>
       <c r="AX3">
-        <v>310.27639405155668</v>
+        <v>310.16435159908474</v>
       </c>
       <c r="AY3">
-        <v>97.126137383957371</v>
+        <v>95.2781125187441</v>
       </c>
       <c r="AZ3">
         <v>105.89248712718322</v>
       </c>
       <c r="BA3">
-        <v>126.37845105399929</v>
+        <v>126.21894563199891</v>
       </c>
       <c r="BB3">
-        <v>1.1879899905508486</v>
+        <v>1.1718156940141815</v>
       </c>
       <c r="BC3">
         <v>1.2502251600686518</v>
       </c>
       <c r="BD3">
-        <v>1.4185041038211952</v>
+        <v>1.4172255417747834</v>
       </c>
       <c r="BE3">
-        <v>90</v>
+        <v>56.14786336650748</v>
       </c>
       <c r="BF3">
         <v>22.5776231769941</v>
       </c>
       <c r="BG3">
-        <v>56.046851702509962</v>
+        <v>54.794785974926533</v>
       </c>
       <c r="BH3">
-        <v>21.409677794180755</v>
+        <v>28.013336007527332</v>
       </c>
       <c r="BI3">
         <v>65.962664482687714</v>
       </c>
       <c r="BJ3">
-        <v>23.133921899746596</v>
+        <v>23.422401978921382</v>
       </c>
       <c r="BK3">
-        <v>44.552986688506955</v>
+        <v>37.949328475160378</v>
       </c>
       <c r="BL3">
         <v>29.119810070153076</v>
       </c>
       <c r="BM3">
-        <v>0.57742315011010747</v>
+        <v>0.44617214605654509</v>
       </c>
     </row>
     <row r="4" spans="1:65">
@@ -1257,31 +1257,31 @@
         <v>338.16075694801106</v>
       </c>
       <c r="U4">
-        <v>353.23686971459057</v>
+        <v>353.1730861018118</v>
       </c>
       <c r="V4">
         <v>359.73134528492022</v>
       </c>
       <c r="W4">
-        <v>369.03744827251916</v>
+        <v>368.35723717588479</v>
       </c>
       <c r="X4">
-        <v>85.766213788746626</v>
+        <v>87.068003720093884</v>
       </c>
       <c r="Y4">
         <v>197.32226861284755</v>
       </c>
       <c r="Z4">
-        <v>70.426617487264849</v>
+        <v>86.444915340129924</v>
       </c>
       <c r="AA4">
-        <v>181.07898811268564</v>
+        <v>178.97210030089858</v>
       </c>
       <c r="AB4">
         <v>69.5616242976259</v>
       </c>
       <c r="AC4">
-        <v>177.14292065897152</v>
+        <v>152.92729296125964</v>
       </c>
       <c r="AD4">
         <v>214.41995491565626</v>
@@ -1293,13 +1293,13 @@
         <v>201.441191743289</v>
       </c>
       <c r="AG4">
-        <v>47.901699647906668</v>
+        <v>50.195285369280967</v>
       </c>
       <c r="AH4">
         <v>185.95319719491755</v>
       </c>
       <c r="AI4">
-        <v>35.143874297832284</v>
+        <v>61.220150588891464</v>
       </c>
       <c r="AJ4">
         <v>71.142607476102043</v>
@@ -1311,85 +1311,85 @@
         <v>61.0312751794986</v>
       </c>
       <c r="AM4">
-        <v>0.26444744976246376</v>
+        <v>0.268461326699123</v>
       </c>
       <c r="AN4">
         <v>0.58351616667094208</v>
       </c>
       <c r="AO4">
-        <v>0.20826372084946646</v>
+        <v>0.2556326053925293</v>
       </c>
       <c r="AP4">
-        <v>0.24280085444660485</v>
+        <v>0.24653068749127205</v>
       </c>
       <c r="AQ4">
         <v>0.54852675809098927</v>
       </c>
       <c r="AR4">
-        <v>0.19083867454897871</v>
+        <v>0.23467684795033317</v>
       </c>
       <c r="AS4">
-        <v>0.5126276548056673</v>
+        <v>0.50675464055407937</v>
       </c>
       <c r="AT4">
         <v>0.19337103983121232</v>
       </c>
       <c r="AU4">
-        <v>0.48001340104692752</v>
+        <v>0.41516027792400689</v>
       </c>
       <c r="AV4">
-        <v>310.27639405155668</v>
+        <v>310.16435159908474</v>
       </c>
       <c r="AW4">
         <v>322.08952585583643</v>
       </c>
       <c r="AX4">
-        <v>338.96972867141631</v>
+        <v>337.72129994235559</v>
       </c>
       <c r="AY4">
-        <v>126.37845105399929</v>
+        <v>126.21894563199891</v>
       </c>
       <c r="AZ4">
         <v>139.19764769616907</v>
       </c>
       <c r="BA4">
-        <v>166.48888186767266</v>
+        <v>164.34965460071388</v>
       </c>
       <c r="BB4">
-        <v>1.4185041038211952</v>
+        <v>1.4172255417747834</v>
       </c>
       <c r="BC4">
         <v>1.5050869773596172</v>
       </c>
       <c r="BD4">
-        <v>1.7105297219569222</v>
+        <v>1.6947929446409555</v>
       </c>
       <c r="BE4">
-        <v>56.046851702509962</v>
+        <v>54.794785974926533</v>
       </c>
       <c r="BF4">
         <v>19.544280221352384</v>
       </c>
       <c r="BG4">
-        <v>60.065206003448516</v>
+        <v>44.9114795174479</v>
       </c>
       <c r="BH4">
-        <v>23.133921899746596</v>
+        <v>23.422401978921382</v>
       </c>
       <c r="BI4">
         <v>71.615404768914814</v>
       </c>
       <c r="BJ4">
-        <v>20.153185293429452</v>
+        <v>23.521106917853185</v>
       </c>
       <c r="BK4">
-        <v>48.481482869168211</v>
+        <v>48.193002789993429</v>
       </c>
       <c r="BL4">
         <v>36.048268954182348</v>
       </c>
       <c r="BM4">
-        <v>0.44625149277058707</v>
+        <v>0.44082047684335879</v>
       </c>
     </row>
     <row r="5" spans="1:65">
@@ -1454,7 +1454,7 @@
         <v>347.8962286942031</v>
       </c>
       <c r="U5">
-        <v>369.03744827251916</v>
+        <v>368.35723717588479</v>
       </c>
       <c r="V5">
         <v>372.66665309756803</v>
@@ -1463,7 +1463,7 @@
         <v>379.567641044599</v>
       </c>
       <c r="X5">
-        <v>70.426617487264849</v>
+        <v>86.444915340129924</v>
       </c>
       <c r="Y5">
         <v>177.05690651241471</v>
@@ -1472,7 +1472,7 @@
         <v>72.564135919489715</v>
       </c>
       <c r="AA5">
-        <v>177.14292065897152</v>
+        <v>152.92729296125964</v>
       </c>
       <c r="AB5">
         <v>62.106358547039491</v>
@@ -1490,7 +1490,7 @@
         <v>174.28815576772286</v>
       </c>
       <c r="AG5">
-        <v>35.143874297832284</v>
+        <v>61.220150588891464</v>
       </c>
       <c r="AH5">
         <v>167.08188774140984</v>
@@ -1508,7 +1508,7 @@
         <v>56.148773165138714</v>
       </c>
       <c r="AM5">
-        <v>0.20826372084946646</v>
+        <v>0.2556326053925293</v>
       </c>
       <c r="AN5">
         <v>0.50893597546883951</v>
@@ -1517,7 +1517,7 @@
         <v>0.20857982908251868</v>
       </c>
       <c r="AP5">
-        <v>0.19083867454897871</v>
+        <v>0.23467684795033317</v>
       </c>
       <c r="AQ5">
         <v>0.47510799541825216</v>
@@ -1526,7 +1526,7 @@
         <v>0.19117576967253505</v>
       </c>
       <c r="AS5">
-        <v>0.48001340104692752</v>
+        <v>0.41516027792400689</v>
       </c>
       <c r="AT5">
         <v>0.16665391987938186</v>
@@ -1535,7 +1535,7 @@
         <v>0.3690220017396818</v>
       </c>
       <c r="AV5">
-        <v>338.96972867141631</v>
+        <v>337.72129994235559</v>
       </c>
       <c r="AW5">
         <v>345.96144674903593</v>
@@ -1544,7 +1544,7 @@
         <v>358.89301023674432</v>
       </c>
       <c r="AY5">
-        <v>166.48888186767266</v>
+        <v>164.34965460071388</v>
       </c>
       <c r="AZ5">
         <v>173.68488655089271</v>
@@ -1553,7 +1553,7 @@
         <v>197.57806825354194</v>
       </c>
       <c r="BB5">
-        <v>1.7105297219569222</v>
+        <v>1.6947929446409555</v>
       </c>
       <c r="BC5">
         <v>1.7483993190861489</v>
@@ -1562,7 +1562,7 @@
         <v>1.9172557051837726</v>
       </c>
       <c r="BE5">
-        <v>60.065206003448516</v>
+        <v>44.9114795174479</v>
       </c>
       <c r="BF5">
         <v>19.324060346882469</v>
@@ -1571,7 +1571,7 @@
         <v>50.694673484171432</v>
       </c>
       <c r="BH5">
-        <v>20.153185293429452</v>
+        <v>23.521106917853185</v>
       </c>
       <c r="BI5">
         <v>70.627513833525384</v>
@@ -1580,13 +1580,13 @@
         <v>23.632304849611685</v>
       </c>
       <c r="BK5">
-        <v>50.474328540095932</v>
+        <v>47.10640691567221</v>
       </c>
       <c r="BL5">
         <v>31.370613137288963</v>
       </c>
       <c r="BM5">
-        <v>0.48030544406034537</v>
+        <v>0.41329272178902543</v>
       </c>
     </row>
   </sheetData>
@@ -2315,31 +2315,31 @@
         <v>324.32233271973291</v>
       </c>
       <c r="U3">
-        <v>338.48306208552407</v>
+        <v>337.81399576208912</v>
       </c>
       <c r="V3">
         <v>347.0185132930356</v>
       </c>
       <c r="W3">
-        <v>353.23686971459057</v>
+        <v>353.3682305414178</v>
       </c>
       <c r="X3">
-        <v>83.441196534470748</v>
+        <v>96.006197468743821</v>
       </c>
       <c r="Y3">
         <v>170.58637149278638</v>
       </c>
       <c r="Z3">
-        <v>85.766213788746626</v>
+        <v>83.02015403165926</v>
       </c>
       <c r="AA3">
-        <v>264.3516156546907</v>
+        <v>219.80645705672774</v>
       </c>
       <c r="AB3">
         <v>123.30492609988829</v>
       </c>
       <c r="AC3">
-        <v>215.69021919404003</v>
+        <v>220.52129336715751</v>
       </c>
       <c r="AD3">
         <v>250.83728474878114</v>
@@ -2351,13 +2351,13 @@
         <v>251.52144342899067</v>
       </c>
       <c r="AG3">
-        <v>5.1091309723327304E-15</v>
+        <v>47.484278169761218</v>
       </c>
       <c r="AH3">
         <v>153.25040447078592</v>
       </c>
       <c r="AI3">
-        <v>47.901699647906668</v>
+        <v>42.791066555318523</v>
       </c>
       <c r="AJ3">
         <v>83.441196534470748</v>
@@ -2369,85 +2369,85 @@
         <v>71.142607476102043</v>
       </c>
       <c r="AM3">
-        <v>0.26848825609412141</v>
+        <v>0.30891858701908986</v>
       </c>
       <c r="AN3">
         <v>0.52597787535094187</v>
       </c>
       <c r="AO3">
-        <v>0.26444744976246376</v>
+        <v>0.25598038018369257</v>
       </c>
       <c r="AP3">
-        <v>0.24651513142299503</v>
+        <v>0.2841984011117103</v>
       </c>
       <c r="AQ3">
         <v>0.49157714922470658</v>
       </c>
       <c r="AR3">
-        <v>0.24280085444660485</v>
+        <v>0.23493949612974216</v>
       </c>
       <c r="AS3">
-        <v>0.78098919935880673</v>
+        <v>0.65067303253927322</v>
       </c>
       <c r="AT3">
         <v>0.35532665081694054</v>
       </c>
       <c r="AU3">
-        <v>0.61061071956705448</v>
+        <v>0.624055232778801</v>
       </c>
       <c r="AV3">
-        <v>284.72764761759396</v>
+        <v>283.60313993580581</v>
       </c>
       <c r="AW3">
         <v>299.448381570485</v>
       </c>
       <c r="AX3">
-        <v>310.27639405155668</v>
+        <v>310.50720654981905</v>
       </c>
       <c r="AY3">
-        <v>97.126137383957371</v>
+        <v>95.793399708605349</v>
       </c>
       <c r="AZ3">
         <v>111.61678704621447</v>
       </c>
       <c r="BA3">
-        <v>126.37845105399929</v>
+        <v>126.70749296979982</v>
       </c>
       <c r="BB3">
-        <v>1.1879899905508486</v>
+        <v>1.17633455788332</v>
       </c>
       <c r="BC3">
         <v>1.2981170396729074</v>
       </c>
       <c r="BD3">
-        <v>1.4185041038211952</v>
+        <v>1.4211401780530102</v>
       </c>
       <c r="BE3">
-        <v>90</v>
+        <v>60.35688846084625</v>
       </c>
       <c r="BF3">
         <v>26.054813563599179</v>
       </c>
       <c r="BG3">
-        <v>56.046851702509962</v>
+        <v>58.973808095197313</v>
       </c>
       <c r="BH3">
-        <v>18.399740434061176</v>
+        <v>22.309658940737</v>
       </c>
       <c r="BI3">
         <v>37.4200979581621</v>
       </c>
       <c r="BJ3">
-        <v>19.25888028825614</v>
+        <v>18.820904240164616</v>
       </c>
       <c r="BK3">
-        <v>19.020357524100927</v>
+        <v>15.110439017425108</v>
       </c>
       <c r="BL3">
         <v>29.992038138910786</v>
       </c>
       <c r="BM3">
-        <v>0.6947304340889674</v>
+        <v>0.60014337551291641</v>
       </c>
     </row>
     <row r="4" spans="1:65">
@@ -2512,31 +2512,31 @@
         <v>338.16075694801106</v>
       </c>
       <c r="U4">
-        <v>353.23686971459057</v>
+        <v>353.3682305414178</v>
       </c>
       <c r="V4">
         <v>362.43751394580022</v>
       </c>
       <c r="W4">
-        <v>369.03744827251916</v>
+        <v>368.65479593132704</v>
       </c>
       <c r="X4">
-        <v>85.766213788746626</v>
+        <v>83.02015403165926</v>
       </c>
       <c r="Y4">
         <v>170.72039394703162</v>
       </c>
       <c r="Z4">
-        <v>70.426617487264849</v>
+        <v>79.8377191153506</v>
       </c>
       <c r="AA4">
-        <v>215.69021919404003</v>
+        <v>220.52129336715751</v>
       </c>
       <c r="AB4">
         <v>110.08511203381906</v>
       </c>
       <c r="AC4">
-        <v>213.36811792645818</v>
+        <v>197.77848702772141</v>
       </c>
       <c r="AD4">
         <v>251.52144342899067</v>
@@ -2548,13 +2548,13 @@
         <v>239.59713838878119</v>
       </c>
       <c r="AG4">
-        <v>47.901699647906668</v>
+        <v>42.791066555318523</v>
       </c>
       <c r="AH4">
         <v>157.44194728826497</v>
       </c>
       <c r="AI4">
-        <v>35.143874297832284</v>
+        <v>51.470815454060336</v>
       </c>
       <c r="AJ4">
         <v>71.142607476102043</v>
@@ -2566,85 +2566,85 @@
         <v>61.0312751794986</v>
       </c>
       <c r="AM4">
-        <v>0.26444744976246376</v>
+        <v>0.25598038018369257</v>
       </c>
       <c r="AN4">
         <v>0.50484981015487329</v>
       </c>
       <c r="AO4">
-        <v>0.20826372084946646</v>
+        <v>0.23609398037757784</v>
       </c>
       <c r="AP4">
-        <v>0.24280085444660485</v>
+        <v>0.23493949612974216</v>
       </c>
       <c r="AQ4">
         <v>0.47103400552670593</v>
       </c>
       <c r="AR4">
-        <v>0.19083867454897871</v>
+        <v>0.21656498164809648</v>
       </c>
       <c r="AS4">
-        <v>0.61061071956705448</v>
+        <v>0.624055232778801</v>
       </c>
       <c r="AT4">
         <v>0.303735424171024</v>
       </c>
       <c r="AU4">
-        <v>0.57817470537270377</v>
+        <v>0.53648694987970147</v>
       </c>
       <c r="AV4">
-        <v>310.27639405155668</v>
+        <v>310.50720654981905</v>
       </c>
       <c r="AW4">
         <v>326.95375086100125</v>
       </c>
       <c r="AX4">
-        <v>338.96972867141631</v>
+        <v>338.26714244637833</v>
       </c>
       <c r="AY4">
-        <v>126.37845105399929</v>
+        <v>126.70749296979982</v>
       </c>
       <c r="AZ4">
         <v>146.7059356352807</v>
       </c>
       <c r="BA4">
-        <v>166.48888186767266</v>
+        <v>165.28254301559932</v>
       </c>
       <c r="BB4">
-        <v>1.4185041038211952</v>
+        <v>1.4211401780530102</v>
       </c>
       <c r="BC4">
         <v>1.5626714059803666</v>
       </c>
       <c r="BD4">
-        <v>1.7105297219569222</v>
+        <v>1.7016626849660006</v>
       </c>
       <c r="BE4">
-        <v>56.046851702509962</v>
+        <v>58.973808095197313</v>
       </c>
       <c r="BF4">
         <v>22.74701948422388</v>
       </c>
       <c r="BG4">
-        <v>60.065206003448516</v>
+        <v>49.85734143374728</v>
       </c>
       <c r="BH4">
-        <v>19.25888028825614</v>
+        <v>18.820904240164616</v>
       </c>
       <c r="BI4">
         <v>36.844002558174608</v>
       </c>
       <c r="BJ4">
-        <v>16.62087272371765</v>
+        <v>17.973916019397254</v>
       </c>
       <c r="BK4">
-        <v>17.585122269918465</v>
+        <v>18.023098318009993</v>
       </c>
       <c r="BL4">
         <v>37.318186519224632</v>
       </c>
       <c r="BM4">
-        <v>0.58688468151209539</v>
+        <v>0.59716637685169194</v>
       </c>
     </row>
     <row r="5" spans="1:65">
@@ -2709,7 +2709,7 @@
         <v>347.8962286942031</v>
       </c>
       <c r="U5">
-        <v>369.03744827251916</v>
+        <v>368.65479593132704</v>
       </c>
       <c r="V5">
         <v>375.04624111446373</v>
@@ -2718,7 +2718,7 @@
         <v>379.76047341080232</v>
       </c>
       <c r="X5">
-        <v>70.426617487264849</v>
+        <v>79.8377191153506</v>
       </c>
       <c r="Y5">
         <v>149.69670538425541</v>
@@ -2727,7 +2727,7 @@
         <v>67.304041573884462</v>
       </c>
       <c r="AA5">
-        <v>213.36811792645818</v>
+        <v>197.77848702772141</v>
       </c>
       <c r="AB5">
         <v>107.29485630755799</v>
@@ -2745,7 +2745,7 @@
         <v>215.8806213109188</v>
       </c>
       <c r="AG5">
-        <v>35.143874297832284</v>
+        <v>51.470815454060336</v>
       </c>
       <c r="AH5">
         <v>137.75453774880765</v>
@@ -2763,7 +2763,7 @@
         <v>56.148773165138714</v>
       </c>
       <c r="AM5">
-        <v>0.20826372084946646</v>
+        <v>0.23609398037757784</v>
       </c>
       <c r="AN5">
         <v>0.43029125652246475</v>
@@ -2772,7 +2772,7 @@
         <v>0.19346010684422785</v>
       </c>
       <c r="AP5">
-        <v>0.19083867454897871</v>
+        <v>0.21656498164809648</v>
       </c>
       <c r="AQ5">
         <v>0.39914199630271224</v>
@@ -2781,7 +2781,7 @@
         <v>0.17722761131351064</v>
       </c>
       <c r="AS5">
-        <v>0.57817470537270377</v>
+        <v>0.53648694987970147</v>
       </c>
       <c r="AT5">
         <v>0.28608433986360554</v>
@@ -2790,7 +2790,7 @@
         <v>0.49341887209766067</v>
       </c>
       <c r="AV5">
-        <v>338.96972867141631</v>
+        <v>338.26714244637833</v>
       </c>
       <c r="AW5">
         <v>350.39368688188284</v>
@@ -2799,7 +2799,7 @@
         <v>359.25776086539918</v>
       </c>
       <c r="AY5">
-        <v>166.48888186767266</v>
+        <v>165.28254301559932</v>
       </c>
       <c r="AZ5">
         <v>181.62685749265097</v>
@@ -2808,7 +2808,7 @@
         <v>198.28425061834395</v>
       </c>
       <c r="BB5">
-        <v>1.7105297219569222</v>
+        <v>1.7016626849660006</v>
       </c>
       <c r="BC5">
         <v>1.8052198486722362</v>
@@ -2817,7 +2817,7 @@
         <v>1.9221548222195981</v>
       </c>
       <c r="BE5">
-        <v>60.065206003448516</v>
+        <v>49.85734143374728</v>
       </c>
       <c r="BF5">
         <v>23.041112878882821</v>
@@ -2826,7 +2826,7 @@
         <v>56.538404912590543</v>
       </c>
       <c r="BH5">
-        <v>16.62087272371765</v>
+        <v>17.973916019397254</v>
       </c>
       <c r="BI5">
         <v>33.097509353374683</v>
@@ -2835,13 +2835,13 @@
         <v>17.436602137683902</v>
       </c>
       <c r="BK5">
-        <v>16.476636629657033</v>
+        <v>15.123593333977427</v>
       </c>
       <c r="BL5">
         <v>33.497292033707723</v>
       </c>
       <c r="BM5">
-        <v>0.62995575471954179</v>
+        <v>0.59501216821473868</v>
       </c>
     </row>
   </sheetData>
@@ -3570,31 +3570,31 @@
         <v>324.32233271973291</v>
       </c>
       <c r="U3">
-        <v>338.48306208552407</v>
+        <v>337.960554183575</v>
       </c>
       <c r="V3">
         <v>348.4842458536537</v>
       </c>
       <c r="W3">
-        <v>353.23686971459057</v>
+        <v>353.47956557676991</v>
       </c>
       <c r="X3">
-        <v>83.441196534470748</v>
+        <v>93.400583342848378</v>
       </c>
       <c r="Y3">
         <v>154.94913749291521</v>
       </c>
       <c r="Z3">
-        <v>85.766213788746626</v>
+        <v>80.618690109959672</v>
       </c>
       <c r="AA3">
-        <v>295.82526805916694</v>
+        <v>255.83621734078372</v>
       </c>
       <c r="AB3">
         <v>166.05033234022457</v>
       </c>
       <c r="AC3">
-        <v>246.40554444320748</v>
+        <v>255.9761463232465</v>
       </c>
       <c r="AD3">
         <v>283.81359365466238</v>
@@ -3606,13 +3606,13 @@
         <v>283.81359365466238</v>
       </c>
       <c r="AG3">
-        <v>5.1091309723327304E-15</v>
+        <v>41.967078641242033</v>
       </c>
       <c r="AH3">
         <v>135.62894802063056</v>
       </c>
       <c r="AI3">
-        <v>47.901699647906668</v>
+        <v>37.922323195539839</v>
       </c>
       <c r="AJ3">
         <v>83.441196534470748</v>
@@ -3624,85 +3624,85 @@
         <v>71.142607476102043</v>
       </c>
       <c r="AM3">
-        <v>0.26848825609412141</v>
+        <v>0.30053451749742532</v>
       </c>
       <c r="AN3">
         <v>0.47776277443963872</v>
       </c>
       <c r="AO3">
-        <v>0.26444744976246376</v>
+        <v>0.2485758209553435</v>
       </c>
       <c r="AP3">
-        <v>0.24651513142299503</v>
+        <v>0.27636533964290583</v>
       </c>
       <c r="AQ3">
         <v>0.44463742432128844</v>
       </c>
       <c r="AR3">
-        <v>0.24280085444660485</v>
+        <v>0.22807171322170994</v>
       </c>
       <c r="AS3">
-        <v>0.87397362289407909</v>
+        <v>0.75700023027485452</v>
       </c>
       <c r="AT3">
         <v>0.47649308201426582</v>
       </c>
       <c r="AU3">
-        <v>0.69756462467323688</v>
+        <v>0.72416108666867962</v>
       </c>
       <c r="AV3">
-        <v>284.72764761759396</v>
+        <v>283.84927209888076</v>
       </c>
       <c r="AW3">
         <v>301.98333668221062</v>
       </c>
       <c r="AX3">
-        <v>310.27639405155668</v>
+        <v>310.70289916637654</v>
       </c>
       <c r="AY3">
-        <v>97.126137383957371</v>
+        <v>96.083986569790866</v>
       </c>
       <c r="AZ3">
         <v>114.95586765629335</v>
       </c>
       <c r="BA3">
-        <v>126.37845105399929</v>
+        <v>126.98694743576179</v>
       </c>
       <c r="BB3">
-        <v>1.1879899905508486</v>
+        <v>1.1788798183979889</v>
       </c>
       <c r="BC3">
         <v>1.3257281201909439</v>
       </c>
       <c r="BD3">
-        <v>1.4185041038211952</v>
+        <v>1.4233774521633402</v>
       </c>
       <c r="BE3">
-        <v>90</v>
+        <v>63.299710186010408</v>
       </c>
       <c r="BF3">
         <v>28.917994714645651</v>
       </c>
       <c r="BG3">
-        <v>56.046851702509962</v>
+        <v>61.940306177798583</v>
       </c>
       <c r="BH3">
-        <v>16.383336134869744</v>
+        <v>19.035312707559683</v>
       </c>
       <c r="BI3">
         <v>26.822587171948527</v>
       </c>
       <c r="BJ3">
-        <v>16.781436630583652</v>
+        <v>16.136503012695393</v>
       </c>
       <c r="BK3">
-        <v>10.439251037078781</v>
+        <v>7.7872744643888439</v>
       </c>
       <c r="BL3">
         <v>30.257075357393141</v>
       </c>
       <c r="BM3">
-        <v>0.76105980993697464</v>
+        <v>0.68712558060561535</v>
       </c>
     </row>
     <row r="4" spans="1:65">
@@ -3767,31 +3767,31 @@
         <v>338.16075694801106</v>
       </c>
       <c r="U4">
-        <v>353.23686971459057</v>
+        <v>353.47956557676991</v>
       </c>
       <c r="V4">
         <v>363.94062130706953</v>
       </c>
       <c r="W4">
-        <v>369.03744827251916</v>
+        <v>368.81734684120164</v>
       </c>
       <c r="X4">
-        <v>85.766213788746626</v>
+        <v>80.618690109959672</v>
       </c>
       <c r="Y4">
         <v>153.86902466005486</v>
       </c>
       <c r="Z4">
-        <v>70.426617487264849</v>
+        <v>75.983601777626589</v>
       </c>
       <c r="AA4">
-        <v>246.40554444320748</v>
+        <v>255.9761463232465</v>
       </c>
       <c r="AB4">
         <v>154.01133993823618</v>
       </c>
       <c r="AC4">
-        <v>245.03929968445627</v>
+        <v>235.25307919274957</v>
       </c>
       <c r="AD4">
         <v>283.81359365466238</v>
@@ -3803,13 +3803,13 @@
         <v>272.4610499084759</v>
       </c>
       <c r="AG4">
-        <v>47.901699647906668</v>
+        <v>37.922323195539839</v>
       </c>
       <c r="AH4">
         <v>138.98989389998002</v>
       </c>
       <c r="AI4">
-        <v>35.143874297832284</v>
+        <v>45.262469984140928</v>
       </c>
       <c r="AJ4">
         <v>71.142607476102043</v>
@@ -3821,85 +3821,85 @@
         <v>61.0312751794986</v>
       </c>
       <c r="AM4">
-        <v>0.26444744976246376</v>
+        <v>0.2485758209553435</v>
       </c>
       <c r="AN4">
         <v>0.45501738891515059</v>
       </c>
       <c r="AO4">
-        <v>0.20826372084946646</v>
+        <v>0.2246966870532181</v>
       </c>
       <c r="AP4">
-        <v>0.24280085444660485</v>
+        <v>0.22807171322170994</v>
       </c>
       <c r="AQ4">
         <v>0.42278606907754368</v>
       </c>
       <c r="AR4">
-        <v>0.19083867454897871</v>
+        <v>0.20601959866693084</v>
       </c>
       <c r="AS4">
-        <v>0.69756462467323688</v>
+        <v>0.72416108666867962</v>
       </c>
       <c r="AT4">
         <v>0.42317710890615695</v>
       </c>
       <c r="AU4">
-        <v>0.66399575661358</v>
+        <v>0.6378579565403153</v>
       </c>
       <c r="AV4">
-        <v>310.27639405155668</v>
+        <v>310.70289916637654</v>
       </c>
       <c r="AW4">
         <v>329.67127119938988</v>
       </c>
       <c r="AX4">
-        <v>338.96972867141631</v>
+        <v>338.56551238376119</v>
       </c>
       <c r="AY4">
-        <v>126.37845105399929</v>
+        <v>126.98694743576179</v>
       </c>
       <c r="AZ4">
         <v>151.02434149969008</v>
       </c>
       <c r="BA4">
-        <v>166.48888186767266</v>
+        <v>165.79407761584392</v>
       </c>
       <c r="BB4">
-        <v>1.4185041038211952</v>
+        <v>1.4233774521633402</v>
       </c>
       <c r="BC4">
         <v>1.59540942006844</v>
       </c>
       <c r="BD4">
-        <v>1.7105297219569222</v>
+        <v>1.7054249007640661</v>
       </c>
       <c r="BE4">
-        <v>56.046851702509962</v>
+        <v>61.940306177798583</v>
       </c>
       <c r="BF4">
         <v>25.404710492726185</v>
       </c>
       <c r="BG4">
-        <v>60.065206003448516</v>
+        <v>53.438353131294996</v>
       </c>
       <c r="BH4">
-        <v>16.781436630583652</v>
+        <v>16.136503012695393</v>
       </c>
       <c r="BI4">
         <v>25.379567845421146</v>
       </c>
       <c r="BJ4">
-        <v>14.422326295513601</v>
+        <v>15.036134328126785</v>
       </c>
       <c r="BK4">
-        <v>8.598131214837494</v>
+        <v>9.2430648327257519</v>
       </c>
       <c r="BL4">
         <v>37.738661950314373</v>
       </c>
       <c r="BM4">
-        <v>0.66742363360542556</v>
+        <v>0.685182082214091</v>
       </c>
     </row>
     <row r="5" spans="1:65">
@@ -3964,7 +3964,7 @@
         <v>347.8962286942031</v>
       </c>
       <c r="U5">
-        <v>369.03744827251916</v>
+        <v>368.81734684120164</v>
       </c>
       <c r="V5">
         <v>376.26555446853024</v>
@@ -3973,7 +3973,7 @@
         <v>379.85366304665922</v>
       </c>
       <c r="X5">
-        <v>70.426617487264849</v>
+        <v>75.983601777626589</v>
       </c>
       <c r="Y5">
         <v>133.43960813666479</v>
@@ -3982,7 +3982,7 @@
         <v>64.607666216713014</v>
       </c>
       <c r="AA5">
-        <v>245.03929968445627</v>
+        <v>235.25307919274957</v>
       </c>
       <c r="AB5">
         <v>153.3109342667936</v>
@@ -4000,7 +4000,7 @@
         <v>250.66416591579787</v>
       </c>
       <c r="AG5">
-        <v>35.143874297832284</v>
+        <v>45.262469984140928</v>
       </c>
       <c r="AH5">
         <v>119.88885722682392</v>
@@ -4018,7 +4018,7 @@
         <v>56.148773165138714</v>
       </c>
       <c r="AM5">
-        <v>0.20826372084946646</v>
+        <v>0.2246966870532181</v>
       </c>
       <c r="AN5">
         <v>0.38356152533621374</v>
@@ -4027,7 +4027,7 @@
         <v>0.1857095906420487</v>
       </c>
       <c r="AP5">
-        <v>0.19083867454897871</v>
+        <v>0.20601959866693084</v>
       </c>
       <c r="AQ5">
         <v>0.35464210463045531</v>
@@ -4036,7 +4036,7 @@
         <v>0.17008567377900197</v>
       </c>
       <c r="AS5">
-        <v>0.66399575661358</v>
+        <v>0.6378579565403153</v>
       </c>
       <c r="AT5">
         <v>0.40745407716989435</v>
@@ -4045,7 +4045,7 @@
         <v>0.59443006520409514</v>
       </c>
       <c r="AV5">
-        <v>338.96972867141631</v>
+        <v>338.56551238376119</v>
       </c>
       <c r="AW5">
         <v>352.67572122579168</v>
@@ -4054,7 +4054,7 @@
         <v>359.43409942607479</v>
       </c>
       <c r="AY5">
-        <v>166.48888186767266</v>
+        <v>165.79407761584392</v>
       </c>
       <c r="AZ5">
         <v>185.8156494414562</v>
@@ -4063,7 +4063,7 @@
         <v>198.62630079567148</v>
       </c>
       <c r="BB5">
-        <v>1.7105297219569222</v>
+        <v>1.7054249007640661</v>
       </c>
       <c r="BC5">
         <v>1.8349026521330976</v>
@@ -4072,7 +4072,7 @@
         <v>1.9245259978055951</v>
       </c>
       <c r="BE5">
-        <v>60.065206003448516</v>
+        <v>53.438353131294996</v>
       </c>
       <c r="BF5">
         <v>26.044890876806438</v>
@@ -4081,7 +4081,7 @@
         <v>60.35108496603155</v>
       </c>
       <c r="BH5">
-        <v>14.422326295513601</v>
+        <v>15.036134328126785</v>
       </c>
       <c r="BI5">
         <v>22.467832545300222</v>
@@ -4090,13 +4090,13 @@
         <v>14.398816521047603</v>
       </c>
       <c r="BK5">
-        <v>8.045506249786623</v>
+        <v>7.4316982171734374</v>
       </c>
       <c r="BL5">
         <v>34.306194089225109</v>
       </c>
       <c r="BM5">
-        <v>0.70968939436624323</v>
+        <v>0.69074155275262761</v>
       </c>
     </row>
   </sheetData>
